--- a/NTh/aggregate_Mumberes_results.xlsx
+++ b/NTh/aggregate_Mumberes_results.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,12 +417,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Maize</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Potato</t>
         </is>
@@ -446,322 +434,322 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>63.15208535908484</v>
+        <v>46.47039740744975</v>
       </c>
       <c r="B3" t="n">
-        <v>70.16280682593872</v>
+        <v>53.47742310756423</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>33.21037053537066</v>
+        <v>24.38576205505744</v>
       </c>
       <c r="B4" t="n">
-        <v>36.93048688926708</v>
+        <v>28.08783386102048</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20.8935039711563</v>
+        <v>15.26065772473144</v>
       </c>
       <c r="B5" t="n">
-        <v>23.28636153912444</v>
+        <v>17.6163763252194</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>14.32329224436639</v>
+        <v>10.36330170647119</v>
       </c>
       <c r="B6" t="n">
-        <v>16.02815053688519</v>
+        <v>12.01037346596505</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>10.7264823720309</v>
+        <v>7.657716972046846</v>
       </c>
       <c r="B7" t="n">
-        <v>12.07171055137846</v>
+        <v>8.924585038273056</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8.686201183736415</v>
+        <v>6.10308804817268</v>
       </c>
       <c r="B8" t="n">
-        <v>9.841656309613043</v>
+        <v>7.160420595689075</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7.468538546829644</v>
+        <v>5.159745694161397</v>
       </c>
       <c r="B9" t="n">
-        <v>8.522268281828673</v>
+        <v>6.096686237346887</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6.690180349905243</v>
+        <v>4.545408726975221</v>
       </c>
       <c r="B10" t="n">
-        <v>7.687729202624335</v>
+        <v>5.408672813648896</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6.149850595129972</v>
+        <v>4.11153785067287</v>
       </c>
       <c r="B11" t="n">
-        <v>7.114612521734476</v>
+        <v>4.92567753694586</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5.741420068325041</v>
+        <v>3.779564072136329</v>
       </c>
       <c r="B12" t="n">
-        <v>6.685238380906161</v>
+        <v>4.557535936001263</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>5.408686065075737</v>
+        <v>3.507677508512671</v>
       </c>
       <c r="B13" t="n">
-        <v>6.337391140833101</v>
+        <v>4.256372441587469</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>5.121709818124074</v>
+        <v>3.273434625472499</v>
       </c>
       <c r="B14" t="n">
-        <v>6.038016317775837</v>
+        <v>3.996576185934529</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4.864395351620975</v>
+        <v>3.06461988195367</v>
       </c>
       <c r="B15" t="n">
-        <v>5.769418389099201</v>
+        <v>3.764284238208395</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4.627956951678716</v>
+        <v>2.874434722609905</v>
       </c>
       <c r="B16" t="n">
-        <v>5.522004890074612</v>
+        <v>3.551847388800283</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>4.407479338942797</v>
+        <v>2.698961234162525</v>
       </c>
       <c r="B17" t="n">
-        <v>5.290467435722036</v>
+        <v>3.354914050096947</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>4.200104619303677</v>
+        <v>2.535823367261813</v>
       </c>
       <c r="B18" t="n">
-        <v>5.071769915324718</v>
+        <v>3.170892015814824</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>4.004075740056511</v>
+        <v>2.383479284615684</v>
       </c>
       <c r="B19" t="n">
-        <v>4.864087796256972</v>
+        <v>2.998136067874881</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3.818231192844095</v>
+        <v>2.240846559686953</v>
       </c>
       <c r="B20" t="n">
-        <v>4.666248304222459</v>
+        <v>2.835518220321868</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3.641737580611524</v>
+        <v>2.107103033754626</v>
       </c>
       <c r="B21" t="n">
-        <v>4.477434505439978</v>
+        <v>2.682199794746874</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3.473947637463719</v>
+        <v>1.981580445962341</v>
       </c>
       <c r="B22" t="n">
-        <v>4.297028499981053</v>
+        <v>2.537510027280021</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3.314324460223707</v>
+        <v>1.863707113697714</v>
       </c>
       <c r="B23" t="n">
-        <v>4.124527987642547</v>
+        <v>2.400880955758003</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3.162400721022735</v>
+        <v>1.752976590119677</v>
       </c>
       <c r="B24" t="n">
-        <v>3.95950156535072</v>
+        <v>2.271812079947916</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>3.017756391081965</v>
+        <v>1.648930117062856</v>
       </c>
       <c r="B25" t="n">
-        <v>3.801564496414803</v>
+        <v>2.149850806832859</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2.880006286379782</v>
+        <v>1.551146437678857</v>
       </c>
       <c r="B26" t="n">
-        <v>3.650365323217841</v>
+        <v>2.034581295401381</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2.748792848023494</v>
+        <v>1.459235565570286</v>
       </c>
       <c r="B27" t="n">
-        <v>3.505578243697779</v>
+        <v>1.925617798303274</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2.623781733409155</v>
+        <v>1.372834707935624</v>
       </c>
       <c r="B28" t="n">
-        <v>3.36689856974355</v>
+        <v>1.822600435555131</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2.504658935423663</v>
+        <v>1.291605385618411</v>
       </c>
       <c r="B29" t="n">
-        <v>3.234039849871574</v>
+        <v>1.725192305591425</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2.391128749165361</v>
+        <v>1.215231239709633</v>
       </c>
       <c r="B30" t="n">
-        <v>3.106731905377662</v>
+        <v>1.633077351321726</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2.282912223640802</v>
+        <v>1.143416250616984</v>
       </c>
       <c r="B31" t="n">
-        <v>2.984719381006831</v>
+        <v>1.545958669636103</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2.179745903990598</v>
+        <v>1.075883220728078</v>
       </c>
       <c r="B32" t="n">
-        <v>2.867760597018389</v>
+        <v>1.463557096135787</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2.08138075874372</v>
+        <v>1.012372438251343</v>
       </c>
       <c r="B33" t="n">
-        <v>2.755626587751687</v>
+        <v>1.385609972852014</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1.987581233807077</v>
+        <v>0.9526404752888548</v>
       </c>
       <c r="B34" t="n">
-        <v>2.648100263831973</v>
+        <v>1.31187004714846</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1.898124400060302</v>
+        <v>0.8964590922401309</v>
       </c>
       <c r="B35" t="n">
-        <v>2.544975662820666</v>
+        <v>1.242104471657972</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1.812799174896796</v>
+        <v>0.8436142309557368</v>
       </c>
       <c r="B36" t="n">
-        <v>2.446057267865461</v>
+        <v>1.176093886761303</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1.731405605382037</v>
+        <v>0.7939050848036923</v>
       </c>
       <c r="B37" t="n">
-        <v>2.351159381882686</v>
+        <v>1.113631573538233</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1.653754204729561</v>
+        <v>0.7471432370357812</v>
       </c>
       <c r="B38" t="n">
-        <v>2.260105549138577</v>
+        <v>1.054522668695578</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1.579665336089676</v>
+        <v>0.7031518607804941</v>
       </c>
       <c r="B39" t="n">
-        <v>2.172728018534007</v>
+        <v>0.9985834350731579</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1.508968638992674</v>
+        <v>0.6617649751843354</v>
       </c>
       <c r="B40" t="n">
-        <v>2.088867244300047</v>
+        <v>0.9456405825869467</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1.441502494639674</v>
+        <v>0.6228267530256204</v>
       </c>
       <c r="B41" t="n">
-        <v>2.008371420660486</v>
+        <v>0.8955306353020281</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1.377113526793309</v>
+        <v>0.5861908757100357</v>
       </c>
       <c r="B42" t="n">
-        <v>1.931096047577465</v>
+        <v>0.848099340901039</v>
       </c>
     </row>
   </sheetData>
